--- a/data/employees/EMP021/AST-EMP021-06.xlsx
+++ b/data/employees/EMP021/AST-EMP021-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vendor Comparison - Alex Garcia (Procurement)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Alex Garcia | Role: Senior Engineer | Location: Portland | Date: 2025-02-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>71</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>On-Time %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Quality %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Spend YTD ($K)</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>84</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acme Components</t>
+          <t>EMP021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>97</v>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1450</v>
+        <v>69</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GlobalParts Inc</t>
+          <t>EMP021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mechanical</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>91</v>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
-      </c>
-      <c r="F6" t="n">
-        <v>820</v>
+        <v>63</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TechSupply Co</t>
+          <t>EMP021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>99</v>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2100</v>
+        <v>87</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CleanRoom Solutions</t>
+          <t>EMP021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Consumables</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>88</v>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
-      </c>
-      <c r="F8" t="n">
-        <v>340</v>
+        <v>73</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>98</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>85</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>67</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>96</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>87</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>81</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>64</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>86</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>90</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>72</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>81</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>94</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>85</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>66</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>79</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp021 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>80</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP021</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP021 contributes to ast emp021 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>